--- a/data/trans_orig/LAWTONB_2R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/LAWTONB_2R2-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2007</t>
+          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>90103</t>
+          <t>91382</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>123907</t>
+          <t>123348</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>186384</t>
+          <t>184704</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>233314</t>
+          <t>231434</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>287480</t>
+          <t>289419</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>346933</t>
+          <t>345336</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>35,94%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>249282</t>
+          <t>249841</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>283086</t>
+          <t>281807</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>354435</t>
+          <t>356315</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>401365</t>
+          <t>403045</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>614005</t>
+          <t>615602</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>673458</t>
+          <t>671519</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>69,88%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>8644</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22884</t>
+          <t>22808</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7611</t>
+          <t>7573</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22589</t>
+          <t>21135</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18588</t>
+          <t>18822</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39565</t>
+          <t>38390</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>25,54%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65199</t>
+          <t>65275</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>79190</t>
+          <t>79439</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>39623</t>
+          <t>41077</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>54601</t>
+          <t>54639</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>110730</t>
+          <t>111905</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>131707</t>
+          <t>131473</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,48%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5665</t>
+          <t>5532</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18171</t>
+          <t>18865</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6290</t>
+          <t>6335</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16546</t>
+          <t>16420</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14364</t>
+          <t>14857</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30893</t>
+          <t>32648</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>47,96%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>23023</t>
+          <t>22329</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35529</t>
+          <t>35662</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10335</t>
+          <t>10461</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20591</t>
+          <t>20546</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37182</t>
+          <t>35427</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53711</t>
+          <t>53218</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>78,18%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>114697</t>
+          <t>115143</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>151761</t>
+          <t>152959</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>207894</t>
+          <t>209951</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>257407</t>
+          <t>260274</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>330432</t>
+          <t>332744</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>395194</t>
+          <t>395723</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,56%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>350705</t>
+          <t>349507</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>387769</t>
+          <t>387323</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>419435</t>
+          <t>416568</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>468948</t>
+          <t>466891</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>784114</t>
+          <t>783585</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>848876</t>
+          <t>846564</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,78%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2012</t>
+          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>109426</t>
+          <t>109437</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>148457</t>
+          <t>151622</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>234104</t>
+          <t>233728</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>283599</t>
+          <t>285413</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>350902</t>
+          <t>354703</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>418897</t>
+          <t>419563</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>40,0%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>265941</t>
+          <t>262776</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>304972</t>
+          <t>304961</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>350946</t>
+          <t>349132</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>400441</t>
+          <t>400817</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>630045</t>
+          <t>629379</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>698040</t>
+          <t>694239</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>66,18%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12689</t>
+          <t>12488</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30299</t>
+          <t>31090</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13254</t>
+          <t>12887</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29495</t>
+          <t>30548</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28962</t>
+          <t>30436</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53991</t>
+          <t>54568</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>27,05%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88366</t>
+          <t>87575</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>105976</t>
+          <t>106177</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53579</t>
+          <t>52526</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>69820</t>
+          <t>70187</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>147748</t>
+          <t>147171</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>172777</t>
+          <t>171303</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>84,91%</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>7041</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9472</t>
+          <t>9583</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2272</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13199</t>
+          <t>12730</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19744</t>
+          <t>19534</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12774</t>
+          <t>12663</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21159</t>
+          <t>21101</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35622</t>
+          <t>36091</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>46549</t>
+          <t>46520</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>129139</t>
+          <t>127667</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>173471</t>
+          <t>172407</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>258432</t>
+          <t>257460</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>313226</t>
+          <t>313589</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>398734</t>
+          <t>400061</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>467848</t>
+          <t>470054</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>36,17%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>386166</t>
+          <t>387230</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>430498</t>
+          <t>431970</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>426639</t>
+          <t>426276</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>481433</t>
+          <t>482405</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>831654</t>
+          <t>829448</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>900768</t>
+          <t>899441</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,21%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2016</t>
+          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>81762</t>
+          <t>81626</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>112689</t>
+          <t>113258</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>191227</t>
+          <t>191830</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>239097</t>
+          <t>240940</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>281903</t>
+          <t>283578</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>340091</t>
+          <t>341357</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,57%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>241212</t>
+          <t>240643</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>272139</t>
+          <t>272275</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>315660</t>
+          <t>313817</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>363530</t>
+          <t>362927</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>568567</t>
+          <t>567301</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>626755</t>
+          <t>625080</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>68,79%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15432</t>
+          <t>15546</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31942</t>
+          <t>33564</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42423</t>
+          <t>41002</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70263</t>
+          <t>70605</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62448</t>
+          <t>62575</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>96297</t>
+          <t>96089</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>160590</t>
+          <t>158968</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>177100</t>
+          <t>176986</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>117811</t>
+          <t>117469</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>145651</t>
+          <t>147072</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>284309</t>
+          <t>284517</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>318158</t>
+          <t>318031</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,56%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11042</t>
+          <t>11267</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3134</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15393</t>
+          <t>15229</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7396</t>
+          <t>6814</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23297</t>
+          <t>22204</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>29,33%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30987</t>
+          <t>30762</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40134</t>
+          <t>40115</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18281</t>
+          <t>18445</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30540</t>
+          <t>30204</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>52406</t>
+          <t>53499</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>68307</t>
+          <t>68889</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>91,0%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>107307</t>
+          <t>105007</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>144677</t>
+          <t>141517</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>246635</t>
+          <t>251020</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>307270</t>
+          <t>305776</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>366790</t>
+          <t>368057</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>439137</t>
+          <t>437509</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,05%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>443786</t>
+          <t>446946</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>481156</t>
+          <t>483456</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>469235</t>
+          <t>470729</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>529870</t>
+          <t>525485</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>925831</t>
+          <t>927459</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>998178</t>
+          <t>996911</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,04%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2023</t>
+          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>88350</t>
+          <t>89763</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>115384</t>
+          <t>115665</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>249012</t>
+          <t>248819</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>281018</t>
+          <t>279511</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>344540</t>
+          <t>345790</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>385888</t>
+          <t>388446</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>50,86%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>150445</t>
+          <t>150164</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>177479</t>
+          <t>176066</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>216871</t>
+          <t>218378</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>248877</t>
+          <t>249070</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>377830</t>
+          <t>375272</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>419178</t>
+          <t>417928</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>54,72%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>35703</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55591</t>
+          <t>54585</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18546</t>
+          <t>21185</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>112219</t>
+          <t>112528</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45437</t>
+          <t>46521</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>150589</t>
+          <t>150860</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,76%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>217046</t>
+          <t>218052</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>237160</t>
+          <t>236934</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>341798</t>
+          <t>341489</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>435471</t>
+          <t>432832</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>576065</t>
+          <t>575794</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>681217</t>
+          <t>680133</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,6%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10217</t>
+          <t>10018</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22060</t>
+          <t>22010</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9956</t>
+          <t>10593</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19894</t>
+          <t>20078</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23346</t>
+          <t>23747</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38496</t>
+          <t>38414</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81187</t>
+          <t>81237</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93030</t>
+          <t>93229</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51431</t>
+          <t>51247</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61369</t>
+          <t>60732</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>136075</t>
+          <t>136157</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>151225</t>
+          <t>150824</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,4%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>145226</t>
+          <t>143107</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>179702</t>
+          <t>179973</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>177879</t>
+          <t>183313</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>432959</t>
+          <t>429703</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>327415</t>
+          <t>293631</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>581149</t>
+          <t>578944</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,77%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>462010</t>
+          <t>461739</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>496486</t>
+          <t>498605</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>590272</t>
+          <t>593528</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>845352</t>
+          <t>839918</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1083794</t>
+          <t>1085999</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1337528</t>
+          <t>1371312</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>82,36%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/LAWTONB_2R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/LAWTONB_2R2-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>91382</t>
+          <t>90908</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>123348</t>
+          <t>125025</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>184704</t>
+          <t>185792</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>231434</t>
+          <t>232506</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>289419</t>
+          <t>286879</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>345336</t>
+          <t>343583</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>35,75%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>249841</t>
+          <t>248164</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>281807</t>
+          <t>282281</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>356315</t>
+          <t>355243</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>403045</t>
+          <t>401957</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>615602</t>
+          <t>617355</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>671519</t>
+          <t>674059</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>70,15%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8644</t>
+          <t>8620</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22808</t>
+          <t>21732</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7573</t>
+          <t>7435</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21135</t>
+          <t>21801</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18822</t>
+          <t>19211</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38390</t>
+          <t>37956</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65275</t>
+          <t>66351</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>79439</t>
+          <t>79463</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>41077</t>
+          <t>40411</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>54639</t>
+          <t>54777</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>111905</t>
+          <t>112339</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>131473</t>
+          <t>131084</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,22%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5532</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18865</t>
+          <t>18572</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6335</t>
+          <t>6837</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16420</t>
+          <t>16690</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14857</t>
+          <t>14145</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32648</t>
+          <t>31353</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>46,06%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>22329</t>
+          <t>22622</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35662</t>
+          <t>35703</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10461</t>
+          <t>10191</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20546</t>
+          <t>20044</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35427</t>
+          <t>36722</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53218</t>
+          <t>53930</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>79,22%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>115143</t>
+          <t>114256</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>152959</t>
+          <t>153418</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>209951</t>
+          <t>209277</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>260274</t>
+          <t>259970</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>332744</t>
+          <t>334693</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>395723</t>
+          <t>394645</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,46%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>349507</t>
+          <t>349048</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>387323</t>
+          <t>388210</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>416568</t>
+          <t>416872</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>466891</t>
+          <t>467565</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>783585</t>
+          <t>784663</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>846564</t>
+          <t>844615</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,62%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>109437</t>
+          <t>109407</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>151622</t>
+          <t>148160</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>233728</t>
+          <t>231498</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>285413</t>
+          <t>281244</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>354703</t>
+          <t>353528</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>419563</t>
+          <t>420106</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,05%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>262776</t>
+          <t>266238</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>304961</t>
+          <t>304991</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>349132</t>
+          <t>353301</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>400817</t>
+          <t>403047</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>629379</t>
+          <t>628836</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>694239</t>
+          <t>695414</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,3%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12488</t>
+          <t>12766</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31090</t>
+          <t>30324</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12887</t>
+          <t>13856</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30548</t>
+          <t>30815</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30436</t>
+          <t>29610</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54568</t>
+          <t>53600</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,57%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87575</t>
+          <t>88341</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>106177</t>
+          <t>105899</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52526</t>
+          <t>52259</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>70187</t>
+          <t>69218</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>147171</t>
+          <t>148139</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>171303</t>
+          <t>172129</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,32%</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7041</t>
+          <t>6634</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9583</t>
+          <t>10157</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12730</t>
+          <t>12778</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,17%</t>
         </is>
       </c>
     </row>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19534</t>
+          <t>19941</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12663</t>
+          <t>12089</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21101</t>
+          <t>21102</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>36091</t>
+          <t>36043</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>46520</t>
+          <t>45929</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>94,08%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>127667</t>
+          <t>127896</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>172407</t>
+          <t>172620</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>257460</t>
+          <t>256436</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>313589</t>
+          <t>310887</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>400061</t>
+          <t>398452</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>470054</t>
+          <t>468147</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,03%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>387230</t>
+          <t>387017</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>431970</t>
+          <t>431741</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>426276</t>
+          <t>428978</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>482405</t>
+          <t>483429</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>829448</t>
+          <t>831355</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>899441</t>
+          <t>901050</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,34%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>81626</t>
+          <t>81199</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>113258</t>
+          <t>112061</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>191830</t>
+          <t>190508</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>240940</t>
+          <t>240621</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>283578</t>
+          <t>281857</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>341357</t>
+          <t>339199</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,33%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>240643</t>
+          <t>241840</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>272275</t>
+          <t>272702</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>313817</t>
+          <t>314136</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>362927</t>
+          <t>364249</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>567301</t>
+          <t>569459</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>625080</t>
+          <t>626801</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,98%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15546</t>
+          <t>15254</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33564</t>
+          <t>32682</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41002</t>
+          <t>41398</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70605</t>
+          <t>70343</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62575</t>
+          <t>61589</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>96089</t>
+          <t>95329</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,05%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>158968</t>
+          <t>159850</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>176986</t>
+          <t>177278</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>117469</t>
+          <t>117731</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>147072</t>
+          <t>146676</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>284517</t>
+          <t>285277</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>318031</t>
+          <t>319017</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,82%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1914</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11267</t>
+          <t>11680</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15229</t>
+          <t>16170</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6814</t>
+          <t>6519</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22204</t>
+          <t>21740</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>28,72%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30762</t>
+          <t>30349</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40115</t>
+          <t>40280</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18445</t>
+          <t>17504</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30204</t>
+          <t>30368</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53499</t>
+          <t>53963</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>68889</t>
+          <t>69184</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,39%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>105007</t>
+          <t>106689</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>141517</t>
+          <t>143380</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>251020</t>
+          <t>249585</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>305776</t>
+          <t>306789</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>368057</t>
+          <t>367890</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>437509</t>
+          <t>437218</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,03%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>446946</t>
+          <t>445083</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>483456</t>
+          <t>481774</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>470729</t>
+          <t>469716</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>525485</t>
+          <t>526920</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>927459</t>
+          <t>927750</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>996911</t>
+          <t>997078</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,05%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>101533</t>
+          <t>107923</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89763</t>
+          <t>94706</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>115665</t>
+          <t>122625</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>264671</t>
+          <t>284413</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>248819</t>
+          <t>265594</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>279511</t>
+          <t>300823</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>53,16%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>366204</t>
+          <t>392336</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>345790</t>
+          <t>369786</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>388446</t>
+          <t>413606</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,32%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>164296</t>
+          <t>178419</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>150164</t>
+          <t>163717</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>176066</t>
+          <t>191636</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>233218</t>
+          <t>251183</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>218378</t>
+          <t>234773</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>249070</t>
+          <t>270002</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>397514</t>
+          <t>429602</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>375272</t>
+          <t>408332</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>417928</t>
+          <t>452152</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>55,01%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>265829</t>
+          <t>286342</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>265829</t>
+          <t>286342</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>265829</t>
+          <t>286342</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>497889</t>
+          <t>535596</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>497889</t>
+          <t>535596</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>497889</t>
+          <t>535596</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>763718</t>
+          <t>821938</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>763718</t>
+          <t>821938</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>763718</t>
+          <t>821938</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>44985</t>
+          <t>49507</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35703</t>
+          <t>40265</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54585</t>
+          <t>61203</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>59339</t>
+          <t>67532</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21185</t>
+          <t>57914</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>112528</t>
+          <t>79002</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>104324</t>
+          <t>117039</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46521</t>
+          <t>101843</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>150860</t>
+          <t>133077</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>22,99%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>227652</t>
+          <t>253650</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>218052</t>
+          <t>241954</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>236934</t>
+          <t>262892</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>394678</t>
+          <t>208173</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>341489</t>
+          <t>196703</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>432832</t>
+          <t>217791</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>622330</t>
+          <t>461824</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>575794</t>
+          <t>445786</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>680133</t>
+          <t>477020</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>82,41%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>272637</t>
+          <t>303157</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>272637</t>
+          <t>303157</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>272637</t>
+          <t>303157</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>454017</t>
+          <t>275705</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>454017</t>
+          <t>275705</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>454017</t>
+          <t>275705</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>726654</t>
+          <t>578863</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>726654</t>
+          <t>578863</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>726654</t>
+          <t>578863</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15207</t>
+          <t>16572</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10018</t>
+          <t>11058</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22010</t>
+          <t>24365</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14949</t>
+          <t>16787</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10593</t>
+          <t>12181</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20078</t>
+          <t>23317</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>30156</t>
+          <t>33359</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23747</t>
+          <t>25954</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38414</t>
+          <t>43164</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,58%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>88040</t>
+          <t>100546</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81237</t>
+          <t>92753</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>93229</t>
+          <t>106060</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>56376</t>
+          <t>66068</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51247</t>
+          <t>59538</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60732</t>
+          <t>70674</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>144415</t>
+          <t>166614</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>136157</t>
+          <t>156809</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>150824</t>
+          <t>174019</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>87,02%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>103247</t>
+          <t>117118</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>103247</t>
+          <t>117118</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>103247</t>
+          <t>117118</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>174571</t>
+          <t>199973</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>174571</t>
+          <t>199973</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>174571</t>
+          <t>199973</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>161726</t>
+          <t>174002</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>143107</t>
+          <t>155566</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>179973</t>
+          <t>193700</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>338959</t>
+          <t>368731</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>183313</t>
+          <t>347117</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>429703</t>
+          <t>391273</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,13%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>500685</t>
+          <t>542733</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>293631</t>
+          <t>514989</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>578944</t>
+          <t>575924</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>35,98%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>479986</t>
+          <t>532615</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>461739</t>
+          <t>512917</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>498605</t>
+          <t>551051</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>684272</t>
+          <t>525425</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>593528</t>
+          <t>502883</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>839918</t>
+          <t>547039</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1164258</t>
+          <t>1058040</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1085999</t>
+          <t>1024849</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1371312</t>
+          <t>1085784</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>67,83%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>641712</t>
+          <t>706617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>641712</t>
+          <t>706617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>641712</t>
+          <t>706617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1023231</t>
+          <t>894156</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1023231</t>
+          <t>894156</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1023231</t>
+          <t>894156</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1664943</t>
+          <t>1600773</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1664943</t>
+          <t>1600773</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1664943</t>
+          <t>1600773</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
